--- a/output/pdf_financials_xlsx/VBNK.xlsx
+++ b/output/pdf_financials_xlsx/VBNK.xlsx
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.024</v>
+        <v>0.048</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.019</v>

--- a/output/pdf_financials_xlsx/VBNK.xlsx
+++ b/output/pdf_financials_xlsx/VBNK.xlsx
@@ -2948,35 +2948,23 @@
       <c r="I46" s="3" t="n">
         <v>139.145</v>
       </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J46" s="3" t="n">
+        <v>257.644</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>271.523</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>88.581</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>132.242</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>225.254</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>581.71</v>
       </c>
     </row>
     <row r="47">
@@ -3088,35 +3076,23 @@
       <c r="I48" s="3" t="n">
         <v>139.145</v>
       </c>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J48" s="3" t="n">
+        <v>257.644</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>271.523</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>88.581</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>132.242</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>225.254</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>581.71</v>
       </c>
     </row>
     <row r="49">
@@ -9849,7 +9825,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11861,7 +11837,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/output/pdf_financials_xlsx/VBNK.xlsx
+++ b/output/pdf_financials_xlsx/VBNK.xlsx
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>0</v>
+        <v>73.226</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>0</v>
@@ -8874,10 +8874,10 @@
         <v>0</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>0</v>
+        <v>114.772</v>
       </c>
     </row>
     <row r="136">
@@ -24239,7 +24239,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -26471,7 +26475,11 @@
           <t>Issuance of common shares, net of issue costs (note 12)</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -27757,7 +27765,11 @@
           <t>Issuance of common shares, net of issue costs (note 13)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
